--- a/prism-examples/csgs/learning/results.xlsx
+++ b/prism-examples/csgs/learning/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angel/Desktop/prism-games/prism-examples/csgs/learning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87A97641-45E5-4A4F-B2D9-4CD7BC3C2473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E01C64-7E6C-CE4D-A580-2C983F9BC0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11580" yWindow="5480" windowWidth="28040" windowHeight="17180" xr2:uid="{10DC5DE2-A7EE-4E41-A7E1-52FAA6DC551A}"/>
+    <workbookView xWindow="22060" yWindow="4860" windowWidth="28040" windowHeight="17180" xr2:uid="{10DC5DE2-A7EE-4E41-A7E1-52FAA6DC551A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,6 +36,91 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>Property</t>
+  </si>
+  <si>
+    <t>Progress</t>
+  </si>
+  <si>
+    <t>Type:        CSG
+Players:     p1 p2
+Modules:     m1 m2 env
+Actions:     [] [safe1] [risky1] [safe2] [risky2]
+Variables:   s
+Rewards:     "r1" "r2"
+Switching to explicit engine, which supports CSGs...
+Building model (engine:explicit)...
+Computing reachable states... 4 states
+Reachable states exploration and model construction done in 0.009 secs.
+Sorting reachable states list...
+Time for model construction: 0.05 seconds.
+Type:        CSG
+Players:     2
+States:      4 (1 initial)
+Transitions: 28
+Choices:     16
+Max/avg:     4/4.00
+Minimum reachability probability is 0
+Lower bound on reachability probability: 0.0
+Episode 1: Resolving exploration RMDP
+Slot (0,1) is now known. Remaining unknown slots: 15
+Episode 112210: Resolving exploration RMDP
+Slot (0,2) is now known. Remaining unknown slots: 14
+Episode 112251: Resolving exploration RMDP
+Slot (0,0) is now known. Remaining unknown slots: 13
+Episode 112296: Resolving exploration RMDP
+Slot (0,3) is now known. Remaining unknown slots: 12
+Episode 112301: Resolving exploration RMDP
+Slot (1,1) is now known. Remaining unknown slots: 11
+Episode 141739: Resolving exploration RMDP
+Slot (1,0) is now known. Remaining unknown slots: 10
+Episode 141813: Resolving exploration RMDP
+Slot (1,3) is now known. Remaining unknown slots: 9
+Episode 141839: Resolving exploration RMDP
+Slot (1,2) is now known. Remaining unknown slots: 8
+Episode 141851: Resolving exploration RMDP
+Slot (3,3) is now known. Remaining unknown slots: 7
+Episode 210668: Resolving exploration RMDP
+Slot (3,2) is now known. Remaining unknown slots: 6
+Episode 210676: Resolving exploration RMDP
+Slot (3,0) is now known. Remaining unknown slots: 5
+Episode 210684: Resolving exploration RMDP
+Slot (3,1) is now known. Remaining unknown slots: 4
+Episode 210809: Resolving exploration RMDP</t>
+  </si>
+  <si>
+    <t>Empirical result</t>
+  </si>
+  <si>
+    <t>Execution time: 901608.654292 milliseconds
+noExactNE=false
+episodes=309245
+robustValue=34.257217774502
+deltaT=0.12499993408928269
+nMin=10904414</t>
+  </si>
+  <si>
+    <t>True value</t>
+  </si>
+  <si>
+    <t>Max/avg (actions): (2,2)/(2.00,2.00)
+Starting bounded equilibria computation (solver=Yices 2.6.4)...
+Precomputation took 0.0 seconds.
+Coalition results (initial state): (17.15,17.15)
+True value: SolveOutcome{found=true, value=34.3}</t>
+  </si>
+  <si>
+    <t>safe risky</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69,8 +154,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,9 +493,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17AF775A-F2BD-D047-9A45-BFBAABA6B630}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/prism-examples/csgs/learning/results.xlsx
+++ b/prism-examples/csgs/learning/results.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angel/Desktop/prism-games/prism-examples/csgs/learning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E01C64-7E6C-CE4D-A580-2C983F9BC0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E30D7F-2655-BD4E-9075-0A21C2A3491A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22060" yWindow="4860" windowWidth="28040" windowHeight="17180" xr2:uid="{10DC5DE2-A7EE-4E41-A7E1-52FAA6DC551A}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{10DC5DE2-A7EE-4E41-A7E1-52FAA6DC551A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Example</t>
   </si>
@@ -47,30 +69,54 @@
     <t>Property</t>
   </si>
   <si>
-    <t>Progress</t>
-  </si>
-  <si>
-    <t>Type:        CSG
-Players:     p1 p2
-Modules:     m1 m2 env
-Actions:     [] [safe1] [risky1] [safe2] [risky2]
-Variables:   s
-Rewards:     "r1" "r2"
-Switching to explicit engine, which supports CSGs...
-Building model (engine:explicit)...
-Computing reachable states... 4 states
-Reachable states exploration and model construction done in 0.009 secs.
-Sorting reachable states list...
-Time for model construction: 0.05 seconds.
-Type:        CSG
-Players:     2
+    <t>True value</t>
+  </si>
+  <si>
+    <t>Max/avg (actions): (2,2)/(2.00,2.00)
+Starting bounded equilibria computation (solver=Yices 2.6.4)...
+Precomputation took 0.0 seconds.
+Coalition results (initial state): (17.15,17.15)
+True value: SolveOutcome{found=true, value=34.3}</t>
+  </si>
+  <si>
+    <t>safe risky</t>
+  </si>
+  <si>
+    <t>Max/avg (actions)</t>
+  </si>
+  <si>
+    <t>(2,2)/(2.00,2.00)</t>
+  </si>
+  <si>
+    <t>found</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>SW</t>
+  </si>
+  <si>
+    <t>(17.15, 17.15)</t>
+  </si>
+  <si>
+    <t>Model info</t>
+  </si>
+  <si>
+    <t>Players:     2
 States:      4 (1 initial)
 Transitions: 28
 Choices:     16
-Max/avg:     4/4.00
-Minimum reachability probability is 0
-Lower bound on reachability probability: 0.0
-Episode 1: Resolving exploration RMDP
+Max/avg:     4/4.00</t>
+  </si>
+  <si>
+    <t>p_reach</t>
+  </si>
+  <si>
+    <t>log</t>
+  </si>
+  <si>
+    <t>Episode 1: Resolving exploration RMDP
 Slot (0,1) is now known. Remaining unknown slots: 15
 Episode 112210: Resolving exploration RMDP
 Slot (0,2) is now known. Remaining unknown slots: 14
@@ -97,38 +143,45 @@
 Episode 210809: Resolving exploration RMDP</t>
   </si>
   <si>
-    <t>Empirical result</t>
-  </si>
-  <si>
-    <t>Execution time: 901608.654292 milliseconds
-noExactNE=false
-episodes=309245
-robustValue=34.257217774502
-deltaT=0.12499993408928269
-nMin=10904414</t>
-  </si>
-  <si>
-    <t>True value</t>
-  </si>
-  <si>
-    <t>Max/avg (actions): (2,2)/(2.00,2.00)
-Starting bounded equilibria computation (solver=Yices 2.6.4)...
-Precomputation took 0.0 seconds.
-Coalition results (initial state): (17.15,17.15)
-True value: SolveOutcome{found=true, value=34.3}</t>
-  </si>
-  <si>
-    <t>safe risky</t>
+    <t>noExactNE</t>
+  </si>
+  <si>
+    <t>episodes</t>
+  </si>
+  <si>
+    <t>robust value</t>
+  </si>
+  <si>
+    <t>deltaT</t>
+  </si>
+  <si>
+    <t>nMin</t>
+  </si>
+  <si>
+    <t>Execution time (ms)</t>
+  </si>
+  <si>
+    <t>Empirical</t>
+  </si>
+  <si>
+    <t>Avg time (s)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -154,9 +207,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -493,59 +558,171 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17AF775A-F2BD-D047-9A45-BFBAABA6B630}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="21" max="21" width="10.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="O2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="153" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>901608.65429199999</v>
+      </c>
+      <c r="F4">
+        <v>1437102.701541</v>
+      </c>
+      <c r="G4">
+        <v>857905.32512499997</v>
+      </c>
+      <c r="H4">
+        <f>AVERAGE(E4:G4)/1000</f>
+        <v>1065.5388936526665</v>
+      </c>
+      <c r="I4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>309245</v>
+      </c>
+      <c r="K4" s="1">
+        <v>34.257217774502003</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0.12499993408928201</v>
+      </c>
+      <c r="M4" s="1">
+        <v>10904414</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" t="s">
         <v>6</v>
       </c>
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R4">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5">
+        <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>7</v>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6">
+        <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <v>4</v>
+    <row r="23" spans="21:21" x14ac:dyDescent="0.2">
+      <c r="U23" cm="1">
+        <f t="array" aca="1" ref="U23" ca="1">+U4:U23</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="E1:M1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/prism-examples/csgs/learning/results.xlsx
+++ b/prism-examples/csgs/learning/results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angel/Desktop/prism-games/prism-examples/csgs/learning/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Angel/Desktop/prism-games/prism-examples/csgs/learning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E30D7F-2655-BD4E-9075-0A21C2A3491A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B653B4-2EE8-554B-A309-54711AC393A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{10DC5DE2-A7EE-4E41-A7E1-52FAA6DC551A}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{10DC5DE2-A7EE-4E41-A7E1-52FAA6DC551A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
   <si>
     <t>Example</t>
   </si>
@@ -98,9 +98,6 @@
   </si>
   <si>
     <t>(17.15, 17.15)</t>
-  </si>
-  <si>
-    <t>Model info</t>
   </si>
   <si>
     <t>Players:     2
@@ -143,15 +140,9 @@
 Episode 210809: Resolving exploration RMDP</t>
   </si>
   <si>
-    <t>noExactNE</t>
-  </si>
-  <si>
     <t>episodes</t>
   </si>
   <si>
-    <t>robust value</t>
-  </si>
-  <si>
     <t>deltaT</t>
   </si>
   <si>
@@ -165,13 +156,216 @@
   </si>
   <si>
     <t>Avg time (s)</t>
+  </si>
+  <si>
+    <t>very_simple</t>
+  </si>
+  <si>
+    <t>Players:     2
+States:      3 (1 initial)
+Transitions: 15
+Choices:     12
+Max/avg:     4/4.00</t>
+  </si>
+  <si>
+    <t>effHorizon</t>
+  </si>
+  <si>
+    <t>CSG info</t>
+  </si>
+  <si>
+    <t>p_stop</t>
+  </si>
+  <si>
+    <t>Slot (0,1) is now known. Remaining unknown slots: 11
+Episode 1576: Resolving exploration RMDP
+Slot (0,2) is now known. Remaining unknown slots: 10
+Episode 1578: Resolving exploration RMDP
+Slot (0,3) is now known. Remaining unknown slots: 9
+Episode 1579: Resolving exploration RMDP
+Slot (0,0) is now known. Remaining unknown slots: 8
+Episode 1584: Resolving exploration RMDP
+Slot (2,0) is now known. Remaining unknown slots: 7
+Episode 1654: Resolving exploration RMDP
+Slot (2,2) is now known. Remaining unknown slots: 6
+Episode 1669: Resolving exploration RMDP
+Slot (2,1) is now known. Remaining unknown slots: 5
+Episode 1671: Resolving exploration RMDP
+Slot (2,3) is now known. Remaining unknown slots: 4
+Episode 1672: Resolving exploration RMDP</t>
+  </si>
+  <si>
+    <t>Robust</t>
+  </si>
+  <si>
+    <t>Point</t>
+  </si>
+  <si>
+    <t>strategy</t>
+  </si>
+  <si>
+    <t>foundNE</t>
+  </si>
+  <si>
+    <t>CSG: $ s:0 -&gt;  $ s:1 -&gt;  $ s:2 -&gt;</t>
+  </si>
+  <si>
+    <t>True CSG</t>
+  </si>
+  <si>
+    <t>(0.0,1.0)</t>
+  </si>
+  <si>
+    <t>dev gain</t>
+  </si>
+  <si>
+    <t>(0.9,0.9)</t>
+  </si>
+  <si>
+    <t>true value</t>
+  </si>
+  <si>
+    <t>Slot (0,1) is now known. Remaining unknown slots: 11
+Episode 341: Resolving exploration RMDP
+Slot (0,0) is now known. Remaining unknown slots: 10
+Episode 346: Resolving exploration RMDP
+Slot (0,3) is now known. Remaining unknown slots: 9
+Episode 347: Resolving exploration RMDP
+Slot (0,2) is now known. Remaining unknown slots: 8
+Episode 351: Resolving exploration RMDP
+Slot (2,0) is now known. Remaining unknown slots: 7
+Episode 819: Resolving exploration RMDP
+Slot (2,2) is now known. Remaining unknown slots: 6
+Episode 820: Resolving exploration RMDP
+Slot (2,1) is now known. Remaining unknown slots: 5
+Episode 825: Resolving exploration RMDP
+Slot (2,3) is now known. Remaining unknown slots: 4
+Episode 827: Resolving exploration RMDP</t>
+  </si>
+  <si>
+    <t>NaN</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>CSG: $ s:0 -&gt;  $ s:1 -&gt;  $ s:2 -&gt;  $ s:3 -&gt;</t>
+  </si>
+  <si>
+    <t>(31.999393886022,31.999393886022)</t>
+  </si>
+  <si>
+    <t>Slot (1,1) is now known. Remaining unknown slots: 15
+Episode 269021: Resolving exploration RMDP
+Slot (1,2) is now known. Remaining unknown slots: 14
+Episode 269030: Resolving exploration RMDP
+Slot (1,3) is now known. Remaining unknown slots: 13
+Episode 269051: Resolving exploration RMDP
+Slot (1,0) is now known. Remaining unknown slots: 12
+Episode 269067: Resolving exploration RMDP
+Slot (0,2) is now known. Remaining unknown slots: 11
+Episode 367960: Resolving exploration RMDP
+Slot (0,3) is now known. Remaining unknown slots: 10
+Episode 368018: Resolving exploration RMDP
+Slot (0,0) is now known. Remaining unknown slots: 9
+Episode 368020: Resolving exploration RMDP
+Slot (0,1) is now known. Remaining unknown slots: 8
+Episode 368131: Resolving exploration RMDP
+Slot (3,1) is now known. Remaining unknown slots: 7
+Episode 426800: Resolving exploration RMDP
+Slot (3,2) is now known. Remaining unknown slots: 6
+Episode 426869: Resolving exploration RMDP
+Slot (3,3) is now known. Remaining unknown slots: 5
+Episode 426898: Resolving exploration RMDP
+Slot (3,0) is now known. Remaining unknown slots: 4
+Episode 426964: Resolving exploration RMDP
+Max/avg (actions): (2,2)/(2.00,2.00)
+Starting equilibria computation (solver=Yices 2.6.4)...
+Checking whether all objectives are reachable...
+Value iteration converged after 212 iterations.
+Precomputation took 0.002 seconds.
+Coalition results (initial state): (31.999393886022,31.999393886022)
+True SolveOutcome{found = true, value = 63.998787772044, strategy = CSG: $ s:0 -&gt;  $ s:1 -&gt;  $ s:2 -&gt;  $ s:3 -&gt; }
+---------------------------------------
+Starting expected reachability...
+target=3, inf=0, rest=1
+Starting value iteration (with Jacobi) ...
+Expected reachability took 0.0 seconds.
+True value of returned strategy: 0.0</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Slot (1,0) is now known. Remaining unknown slots: 15
+Episode 70083: Resolving exploration RMDP
+Slot (1,1) is now known. Remaining unknown slots: 14
+Episode 70087: Resolving exploration RMDP
+Slot (1,2) is now known. Remaining unknown slots: 13
+Episode 70091: Resolving exploration RMDP
+Slot (1,3) is now known. Remaining unknown slots: 12
+Episode 70109: Resolving exploration RMDP
+Slot (0,1) is now known. Remaining unknown slots: 11
+Episode 95616: Resolving exploration RMDP
+Slot (0,3) is now known. Remaining unknown slots: 10
+Episode 95680: Resolving exploration RMDP
+Slot (0,2) is now known. Remaining unknown slots: 9
+Episode 95689: Resolving exploration RMDP
+Slot (0,0) is now known. Remaining unknown slots: 8
+Episode 95702: Resolving exploration RMDP
+Slot (3,1) is now known. Remaining unknown slots: 7
+Episode 110822: Resolving exploration RMDP
+Slot (3,2) is now known. Remaining unknown slots: 6
+Episode 110872: Resolving exploration RMDP
+Slot (3,3) is now known. Remaining unknown slots: 5
+Episode 110887: Resolving exploration RMDP
+Slot (3,0) is now known. Remaining unknown slots: 4
+Episode 110896: Resolving exploration RMDP</t>
+  </si>
+  <si>
+    <t>Type:        CSG
+Players:     2
+States:      4 (1 initial)
+Transitions: 28
+Choices:     16
+Max/avg:     4/4.00
+Max/avg (actions): (2,2)/(2.00,2.00)
+Max/avg (actions): (2,2)/(2.00,2.00)
+Disabling Prob1 precomputation to allow strategy generation
+Value iteration converged after 1 iterations.
+Max/avg (actions): (2,2)/(2.00,2.00)
+Max/avg (actions): (2,2)/(2.00,2.00)
+Disabling Prob1 precomputation to allow strategy generation
+Value iteration converged after 21 iterations.
+Stopping probability: 1.0
+Effective horizon: 4
+Lower bound on reachability probability: 0.0
+...
+Episode 110896: Resolving exploration RMDP
+Max/avg (actions): (2,2)/(2.00,2.00)
+Max/avg (actions): (2,2)/(2.00,2.00)
+Disabling Prob1 precomputation to allow strategy generation
+Exception raised by lpSolve when computing value for state 3. lpSolve status: NUMERIC FAILURE encountered
+Rounding up entries...
+Max/avg (actions): (2,2)/(2.00,2.00)
+Max/avg (actions): (2,2)/(2.00,2.00)
+Disabling Prob1 precomputation to allow strategy generation
+Exception raised by lpSolve when computing value for state 3. lpSolve status: NUMERIC FAILURE encountered
+Rounding up entries...
+Exception in thread "main" Error: No NE found but zero-sum property should always have an NE.
+	at learning.PACLearner.runPacLoop(PACLearner.java:134)
+	at learning.PACLearner.runPacLoop(PACLearner.java:78)
+	at learning.PACLearner.main(PACLearner.java:474)</t>
+  </si>
+  <si>
+    <t>Must disable genStrat to allow Prob1 precomputation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -186,16 +380,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -203,17 +428,145 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -221,8 +574,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -558,170 +961,642 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17AF775A-F2BD-D047-9A45-BFBAABA6B630}">
-  <dimension ref="A1:U23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AF24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="21" max="21" width="10.83203125" customWidth="1"/>
+    <col min="30" max="30" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="E1" s="3" t="s">
+    <row r="1" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="G1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y1" s="19"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19"/>
+      <c r="AB1" s="19"/>
+      <c r="AC1" s="19"/>
+      <c r="AD1" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE1" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="21"/>
+      <c r="Z2" s="21"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="21"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="10"/>
+    </row>
+    <row r="3" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD3" s="24"/>
+      <c r="AE3" s="10"/>
+    </row>
+    <row r="4" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>1039803.2304999999</v>
+      </c>
+      <c r="H4">
+        <v>1059254.9819159999</v>
+      </c>
+      <c r="J4">
+        <f>AVERAGE(G4:I4)/1000</f>
+        <v>1049.5291062079998</v>
+      </c>
+      <c r="K4">
+        <v>157404</v>
+      </c>
+      <c r="L4">
+        <v>0.24999978318660601</v>
+      </c>
+      <c r="M4">
+        <v>8514499</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>0.47178008733537902</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>0.47417129109416301</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>0.47415949683118802</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="2"/>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>901608.65429199999</v>
+      </c>
+      <c r="H5">
+        <v>1437102.701541</v>
+      </c>
+      <c r="I5">
+        <v>857905.32512499997</v>
+      </c>
+      <c r="J5">
+        <f>AVERAGE(G5:I5)/1000</f>
+        <v>1065.5388936526665</v>
+      </c>
+      <c r="K5" s="1">
+        <v>309245</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0.12499993408928201</v>
+      </c>
+      <c r="M5" s="1">
+        <v>10904414</v>
+      </c>
+      <c r="N5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1">
+        <v>34.257217774502003</v>
+      </c>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1">
+        <v>34.257217774502003</v>
+      </c>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="4"/>
+      <c r="Z5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB5">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="AD5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1021007.748375</v>
+      </c>
+      <c r="J6">
+        <f t="shared" ref="J6:J8" si="0">AVERAGE(G6:I6)/1000</f>
+        <v>1021.007748375</v>
+      </c>
+      <c r="K6">
+        <v>157404</v>
+      </c>
+      <c r="L6">
+        <v>0.24999978318660601</v>
+      </c>
+      <c r="M6">
+        <v>8514499</v>
+      </c>
+      <c r="N6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="4"/>
+      <c r="AD6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>4419737.1001249999</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>4419.7371001250003</v>
+      </c>
+      <c r="K7">
+        <v>610332</v>
+      </c>
+      <c r="L7">
+        <v>0.124999986476955</v>
+      </c>
+      <c r="M7">
+        <v>36440064</v>
+      </c>
+      <c r="N7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>62.942359082339998</v>
+      </c>
+      <c r="P7" t="s">
+        <v>40</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>64.037710267616006</v>
+      </c>
+      <c r="U7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y7" s="4"/>
+      <c r="Z7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB7">
+        <v>63.998787772043997</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>7111.4561670000003</v>
+      </c>
+      <c r="H8">
+        <v>7722.7123339999998</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>7.4170842505000003</v>
+      </c>
+      <c r="K8">
+        <v>2298</v>
+      </c>
+      <c r="L8">
+        <v>0.124993330872935</v>
+      </c>
+      <c r="M8">
+        <v>80666</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8" t="s">
+        <v>31</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="9" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>2440.3157500000002</v>
+      </c>
+      <c r="K9">
+        <v>1077</v>
+      </c>
+      <c r="L9">
+        <v>0.12498488928567</v>
+      </c>
+      <c r="M9">
+        <v>14152</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB9">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>2613.098375</v>
+      </c>
+      <c r="K10">
+        <v>1077</v>
+      </c>
+      <c r="L10">
+        <v>0.12498488928567</v>
+      </c>
+      <c r="M10">
+        <v>14152</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1.7594916368260001</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1.799959738878</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB10">
+        <v>1.8</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <v>7679.9757079999999</v>
+      </c>
+      <c r="K11">
+        <v>2298</v>
+      </c>
+      <c r="L11">
+        <v>0.124993330872935</v>
+      </c>
+      <c r="M11">
+        <v>80666</v>
+      </c>
+      <c r="N11" t="b">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" t="s">
-        <v>2</v>
-      </c>
-      <c r="O2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P2" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" t="s">
-        <v>9</v>
-      </c>
-      <c r="U2" t="s">
-        <v>14</v>
+      <c r="O11" t="s">
+        <v>38</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="153" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="4"/>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>901608.65429199999</v>
-      </c>
-      <c r="F4">
-        <v>1437102.701541</v>
-      </c>
-      <c r="G4">
-        <v>857905.32512499997</v>
-      </c>
-      <c r="H4">
-        <f>AVERAGE(E4:G4)/1000</f>
-        <v>1065.5388936526665</v>
-      </c>
-      <c r="I4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1">
-        <v>309245</v>
-      </c>
-      <c r="K4" s="1">
-        <v>34.257217774502003</v>
-      </c>
-      <c r="L4" s="1">
-        <v>0.12499993408928201</v>
-      </c>
-      <c r="M4" s="1">
-        <v>10904414</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O4" t="s">
-        <v>6</v>
-      </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="R4">
-        <v>34.299999999999997</v>
-      </c>
-      <c r="U4" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4"/>
-      <c r="C5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A6" s="3"/>
-      <c r="B6" s="4"/>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="21:21" x14ac:dyDescent="0.2">
-      <c r="U23" cm="1">
-        <f t="array" aca="1" ref="U23" ca="1">+U4:U23</f>
+    <row r="24" spans="30:30" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD24" cm="1">
+        <f t="array" aca="1" ref="AD24" ca="1">+AD5:AD24</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="E1:M1"/>
+  <mergeCells count="14">
+    <mergeCell ref="AE1:AE3"/>
+    <mergeCell ref="X1:AC2"/>
+    <mergeCell ref="AD1:AD3"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="Y4:Y7"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="G1:W1"/>
+    <mergeCell ref="N2:R2"/>
+    <mergeCell ref="S2:W2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/prism-examples/csgs/learning/results.xlsx
+++ b/prism-examples/csgs/learning/results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Angel/Desktop/prism-games/prism-examples/csgs/learning/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angel/Desktop/prism-games/prism-examples/csgs/learning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B653B4-2EE8-554B-A309-54711AC393A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1FA600-A324-384C-AC32-4A9A80517D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{10DC5DE2-A7EE-4E41-A7E1-52FAA6DC551A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22180" windowHeight="28800" xr2:uid="{10DC5DE2-A7EE-4E41-A7E1-52FAA6DC551A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
   <si>
     <t>Example</t>
   </si>
@@ -70,13 +70,6 @@
   </si>
   <si>
     <t>True value</t>
-  </si>
-  <si>
-    <t>Max/avg (actions): (2,2)/(2.00,2.00)
-Starting bounded equilibria computation (solver=Yices 2.6.4)...
-Precomputation took 0.0 seconds.
-Coalition results (initial state): (17.15,17.15)
-True value: SolveOutcome{found=true, value=34.3}</t>
   </si>
   <si>
     <t>safe risky</t>
@@ -359,6 +352,88 @@
   </si>
   <si>
     <t>Must disable genStrat to allow Prob1 precomputation</t>
+  </si>
+  <si>
+    <t>Slot (0,3) is now known. Remaining unknown slots: 11
+Episode 426: Resolving exploration RMDP
+Slot (0,1) is now known. Remaining unknown slots: 10
+Episode 428: Resolving exploration RMDP
+Slot (0,0) is now known. Remaining unknown slots: 9
+Episode 429: Resolving exploration RMDP
+Slot (0,2) is now known. Remaining unknown slots: 8
+Episode 432: Resolving exploration RMDP
+Slot (2,0) is now known. Remaining unknown slots: 7
+Episode 444: Resolving exploration RMDP
+Slot (2,1) is now known. Remaining unknown slots: 6
+Slot (2,3) is now known. Remaining unknown slots: 5
+Episode 454: Resolving exploration RMDP
+Slot (2,2) is now known. Remaining unknown slots: 4
+Episode 459: Resolving exploration RMDP</t>
+  </si>
+  <si>
+    <t>aloha</t>
+  </si>
+  <si>
+    <t>Players:     2
+States:      3 (1 initial)
+Transitions: 12
+Choices:     12
+Max/avg:     4/4.00
+Max/avg (actions): (2,2)/(2.00,2.00)</t>
+  </si>
+  <si>
+    <t>Slot (0,0) is now known. Remaining unknown slots: 11
+Episode 71816: Resolving exploration RMDP
+Slot (0,2) is now known. Remaining unknown slots: 10
+Episode 72025: Resolving exploration RMDP
+Slot (0,1) is now known. Remaining unknown slots: 9
+Episode 72029: Resolving exploration RMDP
+Slot (0,3) is now known. Remaining unknown slots: 8
+Episode 72069: Resolving exploration RMDP
+Slot (1,0) is now known. Remaining unknown slots: 7
+Episode 82727: Resolving exploration RMDP
+Slot (1,3) is now known. Remaining unknown slots: 6
+Episode 82794: Resolving exploration RMDP
+Slot (1,2) is now known. Remaining unknown slots: 5
+Episode 82974: Resolving exploration RMDP
+Slot (1,1) is now known. Remaining unknown slots: 4
+Episode 82994: Resolving exploration RMDP</t>
+  </si>
+  <si>
+    <t>eps</t>
+  </si>
+  <si>
+    <t>confidence</t>
+  </si>
+  <si>
+    <t>$ s:0 -&gt;  $ s:1 -&gt;  $ s:2 -&gt;</t>
+  </si>
+  <si>
+    <t>&lt;&lt;p1&gt;&gt; Pmax=? [ F s=1 ]</t>
+  </si>
+  <si>
+    <t>&lt;&lt;p1:p2&gt;&gt; max=? ( R{"r1"}[F s=1] + R{"r2"}[F s=1] )</t>
+  </si>
+  <si>
+    <t>Slot (0,0) is now known. Remaining unknown slots: 11
+Episode 280039: Resolving exploration RMDP
+Slot (0,2) is now known. Remaining unknown slots: 10
+Episode 280112: Resolving exploration RMDP
+Slot (0,3) is now known. Remaining unknown slots: 9
+Episode 280209: Resolving exploration RMDP
+Slot (0,1) is now known. Remaining unknown slots: 8
+Episode 280307: Resolving exploration RMDP
+Slot (1,0) is now known. Remaining unknown slots: 7
+Episode 323436: Resolving exploration RMDP
+Slot (1,2) is now known. Remaining unknown slots: 6
+Episode 323531: Resolving exploration RMDP
+Slot (1,3) is now known. Remaining unknown slots: 5
+Episode 323728: Resolving exploration RMDP
+Slot (1,1) is now known. Remaining unknown slots: 4
+Episode 323828: Resolving exploration RMDP</t>
+  </si>
+  <si>
+    <t>(0.0,0.0)</t>
   </si>
 </sst>
 </file>
@@ -557,37 +632,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -606,27 +699,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -961,418 +1038,420 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17AF775A-F2BD-D047-9A45-BFBAABA6B630}">
-  <dimension ref="A1:AF24"/>
+  <dimension ref="A1:AH24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="30" max="30" width="10.83203125" customWidth="1"/>
+    <col min="32" max="32" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="G1" s="12" t="s">
+    <row r="1" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="I1" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG1" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" s="22"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="22"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11"/>
+      <c r="AF2" s="13"/>
+      <c r="AG2" s="7"/>
+    </row>
+    <row r="3" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y1" s="19"/>
-      <c r="Z1" s="19"/>
-      <c r="AA1" s="19"/>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="19"/>
-      <c r="AD1" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="AE1" s="10" t="s">
-        <v>43</v>
-      </c>
+      <c r="M3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF3" s="14"/>
+      <c r="AG3" s="7"/>
     </row>
-    <row r="2" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="21"/>
-      <c r="AC2" s="21"/>
-      <c r="AD2" s="23"/>
-      <c r="AE2" s="10"/>
+    <row r="4" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="16">
+        <v>0</v>
+      </c>
+      <c r="D4" s="16">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <v>1039803.2304999999</v>
+      </c>
+      <c r="J4">
+        <v>1059254.9819159999</v>
+      </c>
+      <c r="L4">
+        <f>AVERAGE(I4:K4)/1000</f>
+        <v>1049.5291062079998</v>
+      </c>
+      <c r="M4">
+        <v>157404</v>
+      </c>
+      <c r="N4">
+        <v>0.24999978318660601</v>
+      </c>
+      <c r="O4">
+        <v>8514499</v>
+      </c>
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>0.47178008733537902</v>
+      </c>
+      <c r="U4" t="b">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>0.47417129109416301</v>
+      </c>
+      <c r="AA4" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD4">
+        <v>0.47415949683118802</v>
+      </c>
     </row>
-    <row r="3" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="R3" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="S3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="T3" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="U3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="W3" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="X3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD3" s="24"/>
-      <c r="AE3" s="10"/>
-    </row>
-    <row r="4" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="5">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4">
-        <v>1039803.2304999999</v>
-      </c>
-      <c r="H4">
-        <v>1059254.9819159999</v>
-      </c>
-      <c r="J4">
-        <f>AVERAGE(G4:I4)/1000</f>
-        <v>1049.5291062079998</v>
-      </c>
-      <c r="K4">
-        <v>157404</v>
-      </c>
-      <c r="L4">
-        <v>0.24999978318660601</v>
-      </c>
-      <c r="M4">
-        <v>8514499</v>
-      </c>
-      <c r="N4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>0.47178008733537902</v>
-      </c>
-      <c r="S4" t="b">
-        <v>1</v>
-      </c>
-      <c r="T4">
-        <v>0.47417129109416301</v>
-      </c>
-      <c r="Y4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB4">
-        <v>0.47415949683118802</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="2"/>
+    <row r="5" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="15"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
       <c r="E5">
         <v>2</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>901608.65429199999</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>1437102.701541</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>857905.32512499997</v>
       </c>
-      <c r="J5">
-        <f>AVERAGE(G5:I5)/1000</f>
+      <c r="L5">
+        <f>AVERAGE(I5:K5)/1000</f>
         <v>1065.5388936526665</v>
       </c>
-      <c r="K5" s="1">
+      <c r="M5" s="1">
         <v>309245</v>
       </c>
-      <c r="L5" s="1">
+      <c r="N5" s="1">
         <v>0.12499993408928201</v>
       </c>
-      <c r="M5" s="1">
+      <c r="O5" s="1">
         <v>10904414</v>
       </c>
-      <c r="N5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="1">
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1">
         <v>34.257217774502003</v>
       </c>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="1">
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1">
         <v>34.257217774502003</v>
       </c>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
       <c r="W5" s="1"/>
-      <c r="X5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y5" s="4"/>
-      <c r="Z5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB5">
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="15"/>
+      <c r="AB5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD5">
         <v>34.299999999999997</v>
       </c>
-      <c r="AD5" s="3" t="s">
-        <v>14</v>
+      <c r="AF5" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
+    <row r="6" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6">
         <v>3</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>4</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>1021007.748375</v>
       </c>
-      <c r="J6">
-        <f t="shared" ref="J6:J8" si="0">AVERAGE(G6:I6)/1000</f>
+      <c r="L6">
+        <f t="shared" ref="L6:L8" si="0">AVERAGE(I6:K6)/1000</f>
         <v>1021.007748375</v>
       </c>
-      <c r="K6">
+      <c r="M6">
         <v>157404</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <v>0.24999978318660601</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>8514499</v>
       </c>
-      <c r="N6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="S6" t="b">
-        <v>1</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="4"/>
-      <c r="AD6" s="1" t="s">
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="U6" t="b">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="15"/>
+      <c r="AF6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AE6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF6" s="1" t="s">
-        <v>45</v>
-      </c>
     </row>
-    <row r="7" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="2">
-        <v>1</v>
-      </c>
+    <row r="7" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
       <c r="E7">
         <v>4</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>4</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>4419737.1001249999</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <f t="shared" si="0"/>
         <v>4419.7371001250003</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>610332</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>0.124999986476955</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>36440064</v>
       </c>
-      <c r="N7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7">
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7">
         <v>62.942359082339998</v>
       </c>
-      <c r="P7" t="s">
-        <v>40</v>
-      </c>
-      <c r="S7" t="b">
-        <v>1</v>
-      </c>
-      <c r="T7">
+      <c r="R7" t="s">
+        <v>39</v>
+      </c>
+      <c r="U7" t="b">
+        <v>1</v>
+      </c>
+      <c r="V7">
         <v>64.037710267616006</v>
       </c>
-      <c r="U7" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y7" s="4"/>
-      <c r="Z7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB7">
-        <v>63.998787772043997</v>
+      <c r="W7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA7" s="15"/>
+      <c r="AB7" t="b">
+        <v>1</v>
       </c>
       <c r="AC7" t="s">
         <v>40</v>
       </c>
-      <c r="AD7" s="1" t="s">
-        <v>42</v>
+      <c r="AD7">
+        <v>63.998787772043997</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>21</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
@@ -1381,222 +1460,398 @@
       <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>3</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>7111.4561670000003</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>7722.7123339999998</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <f t="shared" si="0"/>
         <v>7.4170842505000003</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <v>2298</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>0.124993330872935</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>80666</v>
       </c>
-      <c r="N8" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8" t="s">
-        <v>31</v>
-      </c>
-      <c r="R8">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8" t="s">
+        <v>30</v>
+      </c>
+      <c r="T8">
         <v>0</v>
       </c>
-      <c r="S8" t="b">
-        <v>1</v>
-      </c>
-      <c r="T8">
-        <v>1</v>
-      </c>
-      <c r="U8" t="s">
-        <v>31</v>
-      </c>
-      <c r="W8">
+      <c r="U8" t="b">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y8">
         <v>0</v>
       </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z8" t="b">
+      <c r="Z8">
         <v>1</v>
       </c>
       <c r="AA8" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB8">
-        <v>1</v>
-      </c>
-      <c r="AD8" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5"/>
+    <row r="9" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
       <c r="E9">
         <v>2</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>2440.3157500000002</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>1077</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>0.12498488928567</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>14152</v>
       </c>
-      <c r="N9" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="X9">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z9" t="b">
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
         <v>1</v>
       </c>
       <c r="AA9" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB9">
-        <v>1</v>
-      </c>
-      <c r="AD9" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5"/>
+    <row r="10" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="15"/>
+      <c r="B10" s="16"/>
       <c r="E10">
         <v>3</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>2613.098375</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>1077</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>0.12498488928567</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>14152</v>
       </c>
-      <c r="N10" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10">
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10">
         <v>1.7594916368260001</v>
       </c>
-      <c r="S10" t="b">
-        <v>1</v>
-      </c>
-      <c r="T10">
+      <c r="U10" t="b">
+        <v>1</v>
+      </c>
+      <c r="V10">
         <v>1.799959738878</v>
       </c>
-      <c r="Y10" t="s">
-        <v>6</v>
-      </c>
       <c r="AA10" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB10">
+        <v>5</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD10">
         <v>1.8</v>
       </c>
-      <c r="AD10" s="1" t="s">
-        <v>37</v>
+      <c r="AF10" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5"/>
+    <row r="11" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="15"/>
+      <c r="B11" s="16"/>
       <c r="E11">
         <v>4</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>3</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>7679.9757079999999</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>2298</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>0.124993330872935</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>80666</v>
       </c>
-      <c r="N11" t="b">
+      <c r="P11" t="b">
         <v>0</v>
       </c>
-      <c r="O11" t="s">
-        <v>38</v>
-      </c>
-      <c r="S11" t="b">
+      <c r="Q11" t="s">
+        <v>37</v>
+      </c>
+      <c r="U11" t="b">
         <v>0</v>
       </c>
-      <c r="T11" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z11" t="b">
+      <c r="V11" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB11" t="b">
         <v>0</v>
       </c>
-      <c r="AA11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD11" s="1" t="s">
-        <v>26</v>
+      <c r="AC11" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF11" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="24" spans="30:30" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AD24" cm="1">
-        <f t="array" aca="1" ref="AD24" ca="1">+AD5:AD24</f>
+    <row r="12" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="24">
+        <v>1.0000000000287499E-6</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="AF13" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="15">
+        <v>1</v>
+      </c>
+      <c r="D16" s="15">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16">
+        <v>0.1</v>
+      </c>
+      <c r="G16">
+        <v>0.05</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16">
+        <v>41102.628333000001</v>
+      </c>
+      <c r="M16">
+        <v>153416</v>
+      </c>
+      <c r="N16">
+        <v>4.9999926606190501E-2</v>
+      </c>
+      <c r="O16">
+        <v>579269</v>
+      </c>
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>0.99900099900598904</v>
+      </c>
+      <c r="R16" t="s">
+        <v>30</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+      <c r="T16" s="24">
+        <v>9.990009940109559E-4</v>
+      </c>
+      <c r="U16" t="b">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>0.99900099900598904</v>
+      </c>
+      <c r="W16" t="s">
+        <v>30</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="24">
+        <v>9.990009940109559E-4</v>
+      </c>
+      <c r="Z16">
+        <v>0.99900099900598904</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF16" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="25"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17">
+        <v>0.1</v>
+      </c>
+      <c r="G17">
+        <v>0.05</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="I17">
+        <v>178386.926125</v>
+      </c>
+      <c r="M17">
+        <v>602596</v>
+      </c>
+      <c r="N17">
+        <v>2.4999984944146701E-2</v>
+      </c>
+      <c r="O17">
+        <v>2506947</v>
+      </c>
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17" t="s">
+        <v>30</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17" t="b">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17" t="s">
+        <v>30</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF17" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AF24" cm="1">
+        <f t="array" aca="1" ref="AF24" ca="1">+AF5:AF24</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="AE1:AE3"/>
-    <mergeCell ref="X1:AC2"/>
-    <mergeCell ref="AD1:AD3"/>
+  <mergeCells count="19">
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="AG1:AG3"/>
+    <mergeCell ref="Z1:AE2"/>
+    <mergeCell ref="AF1:AF3"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="C4:C7"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="Y4:Y7"/>
+    <mergeCell ref="AA4:AA7"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="B4:B7"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="G1:W1"/>
-    <mergeCell ref="N2:R2"/>
-    <mergeCell ref="S2:W2"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="I1:Y1"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="U2:Y2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/prism-examples/csgs/learning/results.xlsx
+++ b/prism-examples/csgs/learning/results.xlsx
@@ -5,16 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angel/Desktop/prism-games/prism-examples/csgs/learning/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Angel/Desktop/prism-games/prism-examples/csgs/learning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1FA600-A324-384C-AC32-4A9A80517D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122FD99B-5AFE-7D4E-8C38-AA8C37AC6AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22180" windowHeight="28800" xr2:uid="{10DC5DE2-A7EE-4E41-A7E1-52FAA6DC551A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{10DC5DE2-A7EE-4E41-A7E1-52FAA6DC551A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="benchmarks" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="safe_risky2" localSheetId="0">benchmarks!#REF!</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -61,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="69">
   <si>
     <t>Example</t>
   </si>
@@ -435,6 +439,135 @@
   <si>
     <t>(0.0,0.0)</t>
   </si>
+  <si>
+    <t>Type:        CSG
+Players:     2
+States:      3 (1 initial)
+Transitions: 13
+Choices:     12
+Max/avg:     4/4.00
+Max/avg (actions): (2,2)/(2.00,2.00)
+Max/avg (actions): (2,2)/(2.00,2.00)
+Disabling Prob1 precomputation to allow strategy generation
+Value iteration converged after 2 iterations.
+Max/avg (actions): (2,2)/(2.00,2.00)
+Max/avg (actions): (2,2)/(2.00,2.00)
+Disabling Prob1 precomputation to allow strategy generation
+Value iteration converged after 2 iterations.
+Stopping probability: 1.0
+Effective horizon: 3
+Lower bound on reachability probability: 1.0
+Slot (1,0) is now known. Remaining unknown slots: 11
+Episode 75037: Resolving exploration RMDP
+Slot (1,3) is now known. Remaining unknown slots: 10
+Episode 75199: Resolving exploration RMDP
+Slot (1,1) is now known. Remaining unknown slots: 9
+Episode 75338: Resolving exploration RMDP
+Slot (1,2) is now known. Remaining unknown slots: 8
+Episode 75496: Resolving exploration RMDP
+Slot (0,2) is now known. Remaining unknown slots: 7
+Episode 92230: Resolving exploration RMDP
+Slot (0,0) is now known. Remaining unknown slots: 6
+Episode 92319: Resolving exploration RMDP
+Slot (0,1) is now known. Remaining unknown slots: 5
+Episode 92493: Resolving exploration RMDP
+Slot (0,3) is now known. Remaining unknown slots: 4
+Episode 92576: Resolving exploration RMDP
+Max/avg (actions): (2,2)/(2.00,2.00)
+Max/avg (actions): (2,2)/(2.00,2.00)
+Disabling Prob1 precomputation to allow strategy generation
+Value iteration converged after 2 iterations.
+Max/avg (actions): (2,2)/(2.00,2.00)
+Max/avg (actions): (2,2)/(2.00,2.00)
+Disabling Prob1 precomputation to allow strategy generation
+Value iteration converged after 2 iterations.
+---------------------------------------
+Epsilon: 0.1
+Confidence: 0.05
+Execution time: 54381.690167 ms
+Episodes=117666
+DeltaT=0.04999992660619054
+nMin=579269
+---------------------------------------
+Robust SolveOutcome{found = true, value = 0.6650091604107602, strategy = CSG: $ s:0 -&gt;  $ s:1 -&gt;  $ s:2 -&gt; }
+Evaluating robust strategy in true CSG...
+Starting probabilistic reachability...
+target=1, yes=1, no=1, maybe=1
+Starting value iteration (with Jacobi)...
+Value iteration (with Jacobi) took 2 iterations, 4 multiplications and 0.003 seconds.
+Probabilistic reachability took 0.007 seconds.
+True value of learned strategy: 0.6650091604108321
+Value gap: 7.194245199571014E-14
+Starting probabilistic reachability...
+target=1, yes=1, no=1, maybe=1
+Starting value iteration (with Jacobi)...
+Value iteration (with Jacobi) took 2 iterations, 4 multiplications and 0.0 seconds.
+Probabilistic reachability took 0.0 seconds.
+Max deviation gain of learned strategy: 7.194245199571014E-14
+---------------------------------------
+Point SolveOutcome{found = true, value = 0.6671625500336476, strategy = CSG: $ s:0 -&gt;  $ s:1 -&gt;  $ s:2 -&gt; }
+Evaluating point strategy in true CSG...
+Starting probabilistic reachability...
+target=1, yes=1, no=1, maybe=1
+Starting value iteration (with Jacobi)...
+Value iteration (with Jacobi) took 2 iterations, 4 multiplications and 0.0 seconds.
+Probabilistic reachability took 0.0 seconds.
+True value of learned strategy: 0.6671625500335178
+Value gap: -1.297850715786808E-13
+Starting probabilistic reachability...
+target=1, yes=1, no=1, maybe=1
+Starting value iteration (with Jacobi)...
+Value iteration (with Jacobi) took 2 iterations, 4 multiplications and 0.0 seconds.
+Probabilistic reachability took 0.0 seconds.
+Max deviation gain of learned strategy: -1.297850715786808E-13
+---------------------------------------
+Starting probabilistic reachability (until)...
+Max/avg (actions): (2,2)/(2.00,2.00)
+Max/avg (actions): (2,2)/(2.00,2.00)
+Disabling Prob1 precomputation to allow strategy generation
+target=1, yes=1, no=1, maybe=1
+Starting value iteration...
+Value iteration converged after 2 iterations.
+Precomputation took 0.0 seconds.
+True SolveOutcome{found = true, value = 0.6666666666666666, strategy = CSG: $ s:0 -&gt;  $ s:1 -&gt;  $ s:2 -&gt; }</t>
+  </si>
+  <si>
+    <t>$ s:0 -&gt;  $ s:1 -&gt;  $ s:2 -&gt;  $ s:3 -&gt;</t>
+  </si>
+  <si>
+    <t>(0.6,0.4)</t>
+  </si>
+  <si>
+    <t>true SW</t>
+  </si>
+  <si>
+    <t>(0.5,0.5)</t>
+  </si>
+  <si>
+    <t>Infinity</t>
+  </si>
+  <si>
+    <t>value gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$ s:0 -&gt;  $ s:1 -&gt;  $ s:2 -&gt;  $ s:3 -&gt; </t>
+  </si>
+  <si>
+    <t>(Infinity,Infinity)</t>
+  </si>
+  <si>
+    <t>no ne</t>
+  </si>
+  <si>
+    <t>traffic_merge</t>
+  </si>
+  <si>
+    <t>Players:     2
+States:      6 (1 initial)
+Transitions: 28
+Choices:     24
+Max/avg:     4/4.00</t>
+  </si>
 </sst>
 </file>
 
@@ -469,7 +602,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -491,6 +624,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,7 +771,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -648,7 +787,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -672,12 +822,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -699,11 +843,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1037,6 +1183,489 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{251770BD-D1E9-9A40-BF3B-C394ED031BF2}">
+  <dimension ref="A1:AE22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="29" max="29" width="10.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="I1" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD1" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="18"/>
+      <c r="AD2" s="11"/>
+    </row>
+    <row r="3" spans="1:31" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC3" s="19"/>
+      <c r="AD3" s="11"/>
+    </row>
+    <row r="4" spans="1:31" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="27">
+        <v>1.0000000000287499E-6</v>
+      </c>
+      <c r="D4" s="10">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0.1</v>
+      </c>
+      <c r="G4">
+        <v>0.05</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <v>2629848.9424589998</v>
+      </c>
+      <c r="J4">
+        <v>729213</v>
+      </c>
+      <c r="K4">
+        <v>2.49999902220761E-2</v>
+      </c>
+      <c r="L4">
+        <v>8663565</v>
+      </c>
+      <c r="M4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>0.99823896372900001</v>
+      </c>
+      <c r="O4" t="s">
+        <v>58</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1.7610362709999899E-3</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4" t="s">
+        <v>58</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC4" s="1"/>
+    </row>
+    <row r="5" spans="1:31" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="12"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>0.1</v>
+      </c>
+      <c r="G5">
+        <v>0.05</v>
+      </c>
+      <c r="I5">
+        <v>889006.62558300002</v>
+      </c>
+      <c r="J5">
+        <v>350850</v>
+      </c>
+      <c r="K5">
+        <v>2.4999984116478399E-2</v>
+      </c>
+      <c r="L5">
+        <v>2584440</v>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>0.99741497035799997</v>
+      </c>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="T5" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" s="28">
+        <v>1</v>
+      </c>
+      <c r="V5" s="29"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="2"/>
+    </row>
+    <row r="6" spans="1:31" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="12"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>0.1</v>
+      </c>
+      <c r="G6">
+        <v>0.05</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>2583136.8941250001</v>
+      </c>
+      <c r="J6">
+        <v>729213</v>
+      </c>
+      <c r="K6">
+        <v>2.49999902220761E-2</v>
+      </c>
+      <c r="L6">
+        <v>8663565</v>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" t="s">
+        <v>62</v>
+      </c>
+      <c r="O6" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q6" s="28"/>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" t="s">
+        <v>64</v>
+      </c>
+      <c r="V6" t="s">
+        <v>62</v>
+      </c>
+      <c r="W6" s="28"/>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC6" s="1"/>
+      <c r="AE6" s="1"/>
+    </row>
+    <row r="7" spans="1:31" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>0.2</v>
+      </c>
+      <c r="G7">
+        <v>0.05</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="AC7" s="1"/>
+    </row>
+    <row r="8" spans="1:31" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="12"/>
+      <c r="B8" s="10"/>
+      <c r="AC8" s="1"/>
+    </row>
+    <row r="9" spans="1:31" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="12"/>
+      <c r="B9" s="10"/>
+      <c r="AC9" s="1"/>
+    </row>
+    <row r="10" spans="1:31" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="7">
+        <v>3.9999940001190201E-6</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="7"/>
+      <c r="AC11" s="1"/>
+    </row>
+    <row r="14" spans="1:31" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="R14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="AC14" s="1"/>
+      <c r="AD14" s="1"/>
+    </row>
+    <row r="15" spans="1:31" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="AC15" s="1"/>
+    </row>
+    <row r="22" spans="29:29" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC22" cm="1">
+        <f t="array" aca="1" ref="AC22" ca="1">+AC5:AC22</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="I1:X1"/>
+    <mergeCell ref="Y1:AB2"/>
+    <mergeCell ref="AC1:AC3"/>
+    <mergeCell ref="AD1:AD3"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="S2:X2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17AF775A-F2BD-D047-9A45-BFBAABA6B630}">
   <dimension ref="A1:AH24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1045,51 +1674,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="I1" s="18" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="I1" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
-      <c r="X1" s="19"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="8" t="s">
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
-      <c r="AD1" s="9"/>
-      <c r="AE1" s="9"/>
-      <c r="AF1" s="12" t="s">
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="7" t="s">
+      <c r="AG1" s="11" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
@@ -1097,40 +1726,40 @@
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
-      <c r="P2" s="21" t="s">
+      <c r="P2" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="21" t="s">
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
-      <c r="X2" s="22"/>
-      <c r="Y2" s="23"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
-      <c r="AE2" s="11"/>
-      <c r="AF2" s="13"/>
-      <c r="AG2" s="7"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="18"/>
+      <c r="AG2" s="11"/>
     </row>
     <row r="3" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="8" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -1145,11 +1774,11 @@
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
       <c r="L3" s="4" t="s">
         <v>19</v>
       </c>
@@ -1210,20 +1839,20 @@
       <c r="AE3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="7"/>
+      <c r="AF3" s="19"/>
+      <c r="AG3" s="11"/>
     </row>
     <row r="4" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="10">
         <v>0</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="10">
         <v>1</v>
       </c>
       <c r="E4">
@@ -1263,7 +1892,7 @@
       <c r="V4">
         <v>0.47417129109416301</v>
       </c>
-      <c r="AA4" s="15" t="s">
+      <c r="AA4" s="12" t="s">
         <v>5</v>
       </c>
       <c r="AB4" t="b">
@@ -1274,10 +1903,10 @@
       </c>
     </row>
     <row r="5" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
       <c r="E5">
         <v>2</v>
       </c>
@@ -1320,7 +1949,7 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
-      <c r="AA5" s="15"/>
+      <c r="AA5" s="12"/>
       <c r="AB5" t="b">
         <v>1</v>
       </c>
@@ -1335,10 +1964,10 @@
       </c>
     </row>
     <row r="6" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="15"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
       <c r="E6">
         <v>3</v>
       </c>
@@ -1373,7 +2002,7 @@
       <c r="V6">
         <v>1</v>
       </c>
-      <c r="AA6" s="15"/>
+      <c r="AA6" s="12"/>
       <c r="AF6" s="1" t="s">
         <v>43</v>
       </c>
@@ -1385,10 +2014,10 @@
       </c>
     </row>
     <row r="7" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
       <c r="E7">
         <v>4</v>
       </c>
@@ -1429,7 +2058,7 @@
       <c r="W7" t="s">
         <v>39</v>
       </c>
-      <c r="AA7" s="15"/>
+      <c r="AA7" s="12"/>
       <c r="AB7" t="b">
         <v>1</v>
       </c>
@@ -1447,10 +2076,10 @@
       </c>
     </row>
     <row r="8" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="1"/>
@@ -1526,8 +2155,8 @@
       </c>
     </row>
     <row r="9" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="15"/>
-      <c r="B9" s="16"/>
+      <c r="A9" s="12"/>
+      <c r="B9" s="10"/>
       <c r="E9">
         <v>2</v>
       </c>
@@ -1569,8 +2198,8 @@
       </c>
     </row>
     <row r="10" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="15"/>
-      <c r="B10" s="16"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="10"/>
       <c r="E10">
         <v>3</v>
       </c>
@@ -1612,8 +2241,8 @@
       </c>
     </row>
     <row r="11" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="15"/>
-      <c r="B11" s="16"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="10"/>
       <c r="E11">
         <v>4</v>
       </c>
@@ -1660,7 +2289,7 @@
       </c>
     </row>
     <row r="13" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="24">
+      <c r="C13" s="7">
         <v>1.0000000000287499E-6</v>
       </c>
       <c r="E13">
@@ -1674,16 +2303,16 @@
       </c>
     </row>
     <row r="16" spans="1:34" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="12">
+        <v>1</v>
+      </c>
+      <c r="D16" s="12">
         <v>1</v>
       </c>
       <c r="E16" t="s">
@@ -1722,7 +2351,7 @@
       <c r="S16">
         <v>1</v>
       </c>
-      <c r="T16" s="24">
+      <c r="T16" s="7">
         <v>9.990009940109559E-4</v>
       </c>
       <c r="U16" t="b">
@@ -1737,7 +2366,7 @@
       <c r="X16">
         <v>1</v>
       </c>
-      <c r="Y16" s="24">
+      <c r="Y16" s="7">
         <v>9.990009940109559E-4</v>
       </c>
       <c r="Z16">
@@ -1749,12 +2378,15 @@
       <c r="AF16" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="AG16" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="17" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="25"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
       <c r="E17" t="s">
         <v>54</v>
       </c>
@@ -1833,12 +2465,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
     <mergeCell ref="AG1:AG3"/>
     <mergeCell ref="Z1:AE2"/>
     <mergeCell ref="AF1:AF3"/>
@@ -1852,6 +2478,12 @@
     <mergeCell ref="I1:Y1"/>
     <mergeCell ref="P2:T2"/>
     <mergeCell ref="U2:Y2"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
